--- a/raster_cells_per_sub.xlsx
+++ b/raster_cells_per_sub.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\savan\OneDrive - University of Virginia\StreamLit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myuva-my.sharepoint.com/personal/wnt6gp_virginia_edu/Documents/StreamLit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1852C1EA-C39D-4C6D-B25B-A0AA6EB64147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{1852C1EA-C39D-4C6D-B25B-A0AA6EB64147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F42CA0E6-0C1C-4A87-8962-D1A45EB9583A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{97454CBC-327E-48EE-B8D6-214EE2D65EB7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97454CBC-327E-48EE-B8D6-214EE2D65EB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabulat_Subcatc2" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabulat_Subcatc2!$A$1:$X$1</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
   <si>
     <t>NAME</t>
   </si>
@@ -231,6 +232,9 @@
   </si>
   <si>
     <t>Percent_Imp_to_perv</t>
+  </si>
+  <si>
+    <t>MaxNumber_RG</t>
   </si>
 </sst>
 </file>
@@ -630,22 +634,22 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z41"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="3"/>
-    <col min="2" max="2" width="9.81640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="3" customWidth="1"/>
-    <col min="5" max="19" width="10.81640625" style="3"/>
-    <col min="20" max="20" width="10.81640625" style="3" customWidth="1"/>
-    <col min="22" max="22" width="10.81640625" style="3"/>
-    <col min="24" max="24" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.81640625" customWidth="1"/>
-    <col min="26" max="26" width="18.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="10.81640625" style="3"/>
+    <col min="1" max="1" width="10.85546875" style="3"/>
+    <col min="2" max="2" width="9.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="3" customWidth="1"/>
+    <col min="5" max="19" width="10.85546875" style="3"/>
+    <col min="20" max="20" width="10.85546875" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.85546875" style="3"/>
+    <col min="24" max="24" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.85546875" customWidth="1"/>
+    <col min="26" max="26" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="10.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -725,7 +729,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,7 +824,7 @@
         <v>29.074360295380387</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -915,7 +919,7 @@
         <v>31.659951651893635</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1010,7 +1014,7 @@
         <v>14.26272130741612</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,7 +1109,7 @@
         <v>29.256129657847346</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1200,7 +1204,7 @@
         <v>16.613500063799925</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1295,7 +1299,7 @@
         <v>24.813852813852815</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1389,7 +1393,7 @@
         <v>1.2590614269362836</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -1483,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1578,7 +1582,7 @@
         <v>34.043927648578816</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1672,7 +1676,7 @@
         <v>50.314465408805034</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1767,7 +1771,7 @@
         <v>14.471122647631407</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1862,7 +1866,7 @@
         <v>42.993120346809917</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1957,7 +1961,7 @@
         <v>52.388944836074749</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -2052,7 +2056,7 @@
         <v>42.720398200440322</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -2147,7 +2151,7 @@
         <v>39.48231038770205</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -2242,7 +2246,7 @@
         <v>27.456700091157703</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2337,7 +2341,7 @@
         <v>31.130582937811852</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
@@ -2432,7 +2436,7 @@
         <v>53.101736972704714</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
@@ -2527,7 +2531,7 @@
         <v>43.658250146799766</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2622,7 +2626,7 @@
         <v>37.832456799398948</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -2717,7 +2721,7 @@
         <v>40.215414743320743</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>2</v>
       </c>
@@ -2811,7 +2815,7 @@
         <v>12.504765535646206</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -2906,7 +2910,7 @@
         <v>21.750628057649081</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
@@ -3001,7 +3005,7 @@
         <v>32.118834080717491</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,7 +3099,7 @@
         <v>40.313766966331748</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -3190,7 +3194,7 @@
         <v>40.097548453343606</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
@@ -3285,7 +3289,7 @@
         <v>35.57242047472954</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -3380,7 +3384,7 @@
         <v>33.085514142215175</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -3475,7 +3479,7 @@
         <v>33.275032794053345</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -3570,7 +3574,7 @@
         <v>35.95377190754381</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -3665,7 +3669,7 @@
         <v>29.62918944616116</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
@@ -3760,7 +3764,7 @@
         <v>38.374092873023194</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
@@ -3855,7 +3859,7 @@
         <v>32.410846953937593</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -3950,7 +3954,7 @@
         <v>32.011942278984904</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>32</v>
       </c>
@@ -4045,7 +4049,7 @@
         <v>27.475057559478124</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
@@ -4140,7 +4144,7 @@
         <v>42.414752957550448</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -4235,7 +4239,7 @@
         <v>29.56315611242804</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>35</v>
       </c>
@@ -4330,7 +4334,7 @@
         <v>22.821640811916335</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>31</v>
       </c>
@@ -4425,7 +4429,7 @@
         <v>25.863146670588666</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="U41" s="6"/>
       <c r="W41" s="5"/>
     </row>
@@ -4443,4 +4447,459 @@
     <oddFooter>&amp;F</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF97A8AB-3850-455D-BD38-E44BBB953C1C}">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7">
+        <v>60.744334357333329</v>
+      </c>
+      <c r="C2" s="7">
+        <v>15.26753051136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>140.97134653866667</v>
+      </c>
+      <c r="C3" s="7">
+        <v>15.37732239744</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="7">
+        <v>41.333415936000002</v>
+      </c>
+      <c r="C4" s="7">
+        <v>10.053492313600001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7">
+        <v>75.777929216000004</v>
+      </c>
+      <c r="C5" s="7">
+        <v>3.0591033356800006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46.715371136000002</v>
+      </c>
+      <c r="C6" s="7">
+        <v>3.6166738943999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
+        <v>51.415612010666671</v>
+      </c>
+      <c r="C7" s="7">
+        <v>15.930587392000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1.1840301440000001</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="7">
+        <v>94.543013013333336</v>
+      </c>
+      <c r="C10" s="7">
+        <v>33.292774867200002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7">
+        <v>123.42617258666668</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="7">
+        <v>8.0011733973333339</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6.6305688064000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7">
+        <v>163.68319748266669</v>
+      </c>
+      <c r="C13" s="7">
+        <v>52.028437309440008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7">
+        <v>167.98876164266667</v>
+      </c>
+      <c r="C14" s="7">
+        <v>28.055056066560002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="7">
+        <v>480.393321152</v>
+      </c>
+      <c r="C15" s="7">
+        <v>259.08732332800002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="7">
+        <v>125.32779675733335</v>
+      </c>
+      <c r="C16" s="7">
+        <v>62.150818649600005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="7">
+        <v>54.034830208000002</v>
+      </c>
+      <c r="C17" s="7">
+        <v>8.0341827225600007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7">
+        <v>91.780276010666668</v>
+      </c>
+      <c r="C18" s="7">
+        <v>52.947675257599997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="7">
+        <v>92.139073023999998</v>
+      </c>
+      <c r="C19" s="7">
+        <v>3.4875069696000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="7">
+        <v>106.70623176533333</v>
+      </c>
+      <c r="C20" s="7">
+        <v>14.1437782656</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="7">
+        <v>361.34447212800001</v>
+      </c>
+      <c r="C21" s="7">
+        <v>122.05413280767999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="7">
+        <v>103.15414133333333</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3.2420898124800006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="7">
+        <v>11.768542037333333</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7">
+        <v>59.02210869333333</v>
+      </c>
+      <c r="C24" s="7">
+        <v>5.267857749760001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7">
+        <v>164.472550912</v>
+      </c>
+      <c r="C25" s="7">
+        <v>67.667322729600002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="7">
+        <v>82.056876949333329</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="7">
+        <v>224.1763739306667</v>
+      </c>
+      <c r="C27" s="7">
+        <v>26.839810582400002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="7">
+        <v>79.042982037333331</v>
+      </c>
+      <c r="C28" s="7">
+        <v>14.3805842944</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="7">
+        <v>359.26344945066666</v>
+      </c>
+      <c r="C29" s="7">
+        <v>65.659853440000006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="7">
+        <v>163.826716288</v>
+      </c>
+      <c r="C30" s="7">
+        <v>16.867047596799999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="7">
+        <v>101.57543447466666</v>
+      </c>
+      <c r="C31" s="7">
+        <v>9.5971025126400011</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7">
+        <v>89.448095424000002</v>
+      </c>
+      <c r="C32" s="7">
+        <v>36.037572019199999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="7">
+        <v>328.22750779733332</v>
+      </c>
+      <c r="C33" s="7">
+        <v>35.460626421759997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="7">
+        <v>125.22015765333335</v>
+      </c>
+      <c r="C34" s="7">
+        <v>10.075020134399999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="7">
+        <v>69.247823573333335</v>
+      </c>
+      <c r="C35" s="7">
+        <v>36.855629209600004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7">
+        <v>77.069598463999995</v>
+      </c>
+      <c r="C36" s="7">
+        <v>35.8868772736</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="7">
+        <v>43.737355925333333</v>
+      </c>
+      <c r="C37" s="7">
+        <v>36.317433689600001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7">
+        <v>62.645958528000001</v>
+      </c>
+      <c r="C38" s="7">
+        <v>17.825035622399998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="7">
+        <v>106.09627684266667</v>
+      </c>
+      <c r="C39" s="7">
+        <v>30.440338611200001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="7">
+        <v>252.3778191786667</v>
+      </c>
+      <c r="C40" s="7">
+        <v>207.55833146111999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>